--- a/44_心理学/26_浥尘伙伴社团原创：通识教育/000 浥尘伙伴社团通识教育招生广告.xlsx
+++ b/44_心理学/26_浥尘伙伴社团原创：通识教育/000 浥尘伙伴社团通识教育招生广告.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\44_心理学\26_浥尘伙伴社团原创：通识教育\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23C6F19D-6852-4200-984C-DAE5D54119CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C88750-5E19-422F-AB2B-03315E6E673F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F9B5B54B-EA84-4F3E-A518-5A8438F4DD6B}"/>
+    <workbookView xWindow="3075" yWindow="1245" windowWidth="21600" windowHeight="11295" xr2:uid="{F9B5B54B-EA84-4F3E-A518-5A8438F4DD6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="14">
   <si>
     <t>微信公众号@浥尘伙伴社团</t>
   </si>
@@ -83,6 +83,10 @@
   </si>
   <si>
     <t xml:space="preserve">    学习形式：线下（私塾式）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">    &gt;&gt;&gt; 浥尘伙伴社团 / 浥尘读书会</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -173,7 +177,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -183,20 +187,23 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -220,15 +227,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>149600</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>142315</xdr:rowOff>
+      <xdr:colOff>149602</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>142317</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>2606743</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>89340</xdr:rowOff>
+      <xdr:colOff>1992459</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>12939</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -257,8 +264,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="149600" y="3145491"/>
-          <a:ext cx="2457143" cy="2457143"/>
+          <a:off x="149602" y="3369611"/>
+          <a:ext cx="1842857" cy="1842857"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -280,14 +287,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>149600</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>142315</xdr:rowOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>142316</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>2606743</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>89341</xdr:rowOff>
+      <xdr:colOff>1992457</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>12938</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -316,8 +323,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="149600" y="9017374"/>
-          <a:ext cx="2457143" cy="2457143"/>
+          <a:off x="149600" y="9465610"/>
+          <a:ext cx="1842857" cy="1842857"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -655,7 +662,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{338B5F7F-9179-4831-9BD2-4543F06D2573}">
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.625" customWidth="1"/>
@@ -668,55 +675,58 @@
       </c>
       <c r="B1" s="5"/>
     </row>
-    <row r="2" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-    </row>
-    <row r="3" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
-        <v>4</v>
-      </c>
+    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="5"/>
+    </row>
+    <row r="3" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A7" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="3"/>
-    </row>
-    <row r="8" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
-        <v>8</v>
-      </c>
+    <row r="8" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="3"/>
     </row>
     <row r="9" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A12" s="2"/>
     </row>
     <row r="13" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
@@ -727,91 +737,94 @@
     <row r="15" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
-      <c r="B16" s="7" t="s">
-        <v>0</v>
-      </c>
     </row>
     <row r="17" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
       <c r="B17" s="7" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
       <c r="B18" s="7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
       <c r="B19" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A20" s="2"/>
+      <c r="B20" s="7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" s="1"/>
-    </row>
-    <row r="26" spans="1:2" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="5" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="1"/>
+    </row>
+    <row r="27" spans="1:2" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="5"/>
-    </row>
-    <row r="27" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-    </row>
-    <row r="28" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A28" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A29" s="6" t="s">
-        <v>5</v>
-      </c>
+      <c r="B27" s="5"/>
+    </row>
+    <row r="28" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" s="5"/>
+    </row>
+    <row r="29" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
     </row>
     <row r="30" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="3"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A32" s="6" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="33" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A34" s="6" t="s">
-        <v>12</v>
-      </c>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="3"/>
     </row>
     <row r="35" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A37" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A38" s="6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A37" s="2"/>
-    </row>
-    <row r="38" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A38" s="2"/>
     </row>
     <row r="39" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A39" s="2"/>
@@ -819,32 +832,38 @@
     <row r="40" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
     </row>
-    <row r="41" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
-      <c r="B41" s="7" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
-      <c r="B42" s="7" t="s">
-        <v>1</v>
-      </c>
     </row>
     <row r="43" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
       <c r="B43" s="7" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A44" s="2"/>
       <c r="B44" s="7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A45" s="2"/>
+      <c r="B45" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A46" s="2"/>
+      <c r="B46" s="7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A49" s="1"/>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A51" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/44_心理学/26_浥尘伙伴社团原创：通识教育/000 浥尘伙伴社团通识教育招生广告.xlsx
+++ b/44_心理学/26_浥尘伙伴社团原创：通识教育/000 浥尘伙伴社团通识教育招生广告.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\44_心理学\26_浥尘伙伴社团原创：通识教育\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C88750-5E19-422F-AB2B-03315E6E673F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{253F48B3-16CB-47B9-984E-7B4458FA9524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="1245" windowWidth="21600" windowHeight="11295" xr2:uid="{F9B5B54B-EA84-4F3E-A518-5A8438F4DD6B}"/>
+    <workbookView xWindow="6630" yWindow="1200" windowWidth="21600" windowHeight="11295" xr2:uid="{F9B5B54B-EA84-4F3E-A518-5A8438F4DD6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="15">
   <si>
     <t>微信公众号@浥尘伙伴社团</t>
   </si>
@@ -70,23 +70,27 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">    名额限制：寒暑假每期限额2人（需审核，后续可长期学习）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">    报名咨询：请扫描二维码</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">  浥尘伙伴社团通识教育招生</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">    学习形式：线下（私塾式）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">    &gt;&gt;&gt; 浥尘伙伴社团 / 浥尘读书会</t>
+    <t xml:space="preserve">    名额限制：寒暑假每期限额（需审核，后续可长程学习）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">    &gt;&gt;&gt; 浥尘伙伴社团 / 浥尘强学会（个人私塾，非培训机构）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">    教学形式：线下（私塾式）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  招生：心理课/通识教育</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">    参与咨询：请扫描二维码关注</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">    参加咨询：请扫描二维码关注</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -94,7 +98,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -154,6 +158,14 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF333333"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -177,7 +189,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -203,6 +215,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -671,13 +686,13 @@
   <sheetData>
     <row r="1" spans="1:2" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B1" s="5"/>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B2" s="5"/>
     </row>
@@ -685,23 +700,23 @@
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
     </row>
-    <row r="4" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:2" ht="21" x14ac:dyDescent="0.2">
+      <c r="A4" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:2" ht="21" x14ac:dyDescent="0.2">
+      <c r="A5" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:2" ht="21" x14ac:dyDescent="0.2">
+      <c r="A6" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:2" ht="21" x14ac:dyDescent="0.2">
+      <c r="A7" s="9" t="s">
         <v>7</v>
       </c>
     </row>
@@ -715,7 +730,7 @@
     </row>
     <row r="10" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
@@ -725,7 +740,7 @@
     </row>
     <row r="12" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -769,13 +784,13 @@
     </row>
     <row r="27" spans="1:2" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B27" s="5"/>
     </row>
     <row r="28" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B28" s="5"/>
     </row>
@@ -783,23 +798,23 @@
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
     </row>
-    <row r="30" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A30" s="6" t="s">
+    <row r="30" spans="1:2" ht="21" x14ac:dyDescent="0.2">
+      <c r="A30" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A31" s="6" t="s">
+    <row r="31" spans="1:2" ht="21" x14ac:dyDescent="0.2">
+      <c r="A31" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A32" s="6" t="s">
+    <row r="32" spans="1:2" ht="21" x14ac:dyDescent="0.2">
+      <c r="A32" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A33" s="6" t="s">
+    <row r="33" spans="1:2" ht="21" x14ac:dyDescent="0.2">
+      <c r="A33" s="9" t="s">
         <v>7</v>
       </c>
     </row>
@@ -813,7 +828,7 @@
     </row>
     <row r="36" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
@@ -823,7 +838,7 @@
     </row>
     <row r="38" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="15" x14ac:dyDescent="0.2">

--- a/44_心理学/26_浥尘伙伴社团原创：通识教育/000 浥尘伙伴社团通识教育招生广告.xlsx
+++ b/44_心理学/26_浥尘伙伴社团原创：通识教育/000 浥尘伙伴社团通识教育招生广告.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\44_心理学\26_浥尘伙伴社团原创：通识教育\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{253F48B3-16CB-47B9-984E-7B4458FA9524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80740CFC-5E50-4342-8B05-F7C75BD08909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6630" yWindow="1200" windowWidth="21600" windowHeight="11295" xr2:uid="{F9B5B54B-EA84-4F3E-A518-5A8438F4DD6B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F9B5B54B-EA84-4F3E-A518-5A8438F4DD6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
   <si>
     <t>微信公众号@浥尘伙伴社团</t>
   </si>
@@ -91,6 +91,34 @@
   </si>
   <si>
     <t xml:space="preserve">    参加咨询：请扫描二维码关注</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">        ■ 孩子大了为什么会不听父母的话？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">        ■ AI时代需要的真正能力是什么？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">        ■ 为什么孩子们会沉迷手机而不是别的东西？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">        ■ 为什么越来越多的人抑郁躺平？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">        ■ 为什么在网上人们会围观狗吃东西？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  招生：心理/通识教育课堂</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>全国顶级心理学</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -301,14 +329,14 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>149600</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>142316</xdr:rowOff>
+      <xdr:colOff>746872</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>168088</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>1992457</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>12938</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -338,8 +366,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="149600" y="9465610"/>
-          <a:ext cx="1842857" cy="1842857"/>
+          <a:off x="746872" y="10152529"/>
+          <a:ext cx="1245585" cy="1245585"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -677,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{338B5F7F-9179-4831-9BD2-4543F06D2573}">
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B52"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.625" customWidth="1"/>
@@ -784,7 +812,7 @@
     </row>
     <row r="27" spans="1:2" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B27" s="5"/>
     </row>
@@ -800,85 +828,99 @@
     </row>
     <row r="30" spans="1:2" ht="21" x14ac:dyDescent="0.2">
       <c r="A30" s="9" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="21" x14ac:dyDescent="0.2">
       <c r="A31" s="9" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="21" x14ac:dyDescent="0.2">
       <c r="A32" s="9" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="21" x14ac:dyDescent="0.2">
       <c r="A33" s="9" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="3"/>
-    </row>
-    <row r="35" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A35" s="6" t="s">
-        <v>8</v>
+      <c r="A34" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="9" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A39" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A39" s="2"/>
-    </row>
-    <row r="40" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A40" s="2"/>
-    </row>
-    <row r="41" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A41" s="2"/>
-    </row>
-    <row r="42" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A42" s="2"/>
-    </row>
-    <row r="43" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A43" s="2"/>
-      <c r="B43" s="7" t="s">
-        <v>0</v>
+    <row r="40" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A40" s="6"/>
+    </row>
+    <row r="41" spans="1:2" ht="21" x14ac:dyDescent="0.2">
+      <c r="A41" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="21" x14ac:dyDescent="0.2">
+      <c r="A42" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A44" s="2"/>
       <c r="B44" s="7" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A45" s="2"/>
       <c r="B45" s="7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A46" s="2"/>
       <c r="B46" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A47" s="2"/>
+      <c r="B47" s="7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A51" s="1"/>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A52" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/44_心理学/26_浥尘伙伴社团原创：通识教育/000 浥尘伙伴社团通识教育招生广告.xlsx
+++ b/44_心理学/26_浥尘伙伴社团原创：通识教育/000 浥尘伙伴社团通识教育招生广告.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\44_心理学\26_浥尘伙伴社团原创：通识教育\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80740CFC-5E50-4342-8B05-F7C75BD08909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75CEDBD6-6018-43CC-AD48-FD0F0A255CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F9B5B54B-EA84-4F3E-A518-5A8438F4DD6B}"/>
+    <workbookView xWindow="6465" yWindow="675" windowWidth="21600" windowHeight="11295" xr2:uid="{F9B5B54B-EA84-4F3E-A518-5A8438F4DD6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="19">
   <si>
     <t>微信公众号@浥尘伙伴社团</t>
   </si>
@@ -82,26 +82,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">  招生：心理课/通识教育</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">    参与咨询：请扫描二维码关注</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">    参加咨询：请扫描二维码关注</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">        ■ 孩子大了为什么会不听父母的话？</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">        ■ AI时代需要的真正能力是什么？</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">        ■ 为什么孩子们会沉迷手机而不是别的东西？</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -118,7 +102,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>全国顶级心理学</t>
+    <t xml:space="preserve">        ■ 为什么孩子大了会不听父母的话？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">        ■ AI时代真正需要的能力是什么？</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -126,7 +114,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -155,13 +143,6 @@
       <color rgb="FF333333"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF333333"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -194,6 +175,21 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -217,7 +213,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -227,25 +223,28 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -270,74 +269,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>149602</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>142317</xdr:rowOff>
+      <xdr:colOff>627532</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>60320</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>1992459</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>12939</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 1" descr="QR 代码&#10;&#10;AI 生成的内容可能不正确。">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B64E8C99-692E-12A3-EEFD-F154B8D55E6F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="149602" y="3369611"/>
-          <a:ext cx="1842857" cy="1842857"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>746872</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>168088</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1992457</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>12938</xdr:rowOff>
+      <xdr:colOff>1856104</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>78656</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -366,8 +306,67 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="746872" y="10152529"/>
-          <a:ext cx="1245585" cy="1245585"/>
+          <a:off x="627532" y="10123202"/>
+          <a:ext cx="1228572" cy="1228572"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>627532</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>60320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1856104</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>78656</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2" descr="QR 代码&#10;&#10;AI 生成的内容可能不正确。">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{965133D7-6883-46FC-9A17-FE06BA45F3A7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="627532" y="10123202"/>
+          <a:ext cx="1228572" cy="1228572"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -713,97 +712,109 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="4"/>
+    </row>
+    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="4"/>
+    </row>
+    <row r="3" spans="1:2" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+    </row>
+    <row r="4" spans="1:2" ht="21" x14ac:dyDescent="0.2">
+      <c r="A4" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="21" x14ac:dyDescent="0.2">
+      <c r="A5" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="21" x14ac:dyDescent="0.2">
+      <c r="A6" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="21" x14ac:dyDescent="0.2">
+      <c r="A7" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="8"/>
+    </row>
+    <row r="10" spans="1:2" s="10" customFormat="1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A10" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" s="10" customFormat="1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A11" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" s="10" customFormat="1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A12" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" s="10" customFormat="1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A13" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="5"/>
-    </row>
-    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="5"/>
-    </row>
-    <row r="3" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-    </row>
-    <row r="4" spans="1:2" ht="21" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
+    </row>
+    <row r="14" spans="1:2" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="5"/>
+    </row>
+    <row r="15" spans="1:2" ht="21" x14ac:dyDescent="0.2">
+      <c r="A15" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="21" x14ac:dyDescent="0.2">
+      <c r="A16" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="21" x14ac:dyDescent="0.2">
-      <c r="A5" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="21" x14ac:dyDescent="0.2">
-      <c r="A6" s="9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="21" x14ac:dyDescent="0.2">
-      <c r="A7" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="3"/>
-    </row>
-    <row r="9" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A13" s="2"/>
-    </row>
-    <row r="14" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A14" s="2"/>
-    </row>
-    <row r="15" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A15" s="2"/>
-    </row>
-    <row r="16" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A16" s="2"/>
-    </row>
-    <row r="17" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A17" s="2"/>
-      <c r="B17" s="7" t="s">
-        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
-      <c r="B18" s="7" t="s">
-        <v>1</v>
+      <c r="B18" s="6" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
-      <c r="B19" s="7" t="s">
-        <v>2</v>
+      <c r="B19" s="6" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A21" s="2"/>
+      <c r="B21" s="6" t="s">
         <v>3</v>
       </c>
     </row>
@@ -811,111 +822,109 @@
       <c r="A25" s="1"/>
     </row>
     <row r="27" spans="1:2" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B27" s="5"/>
+      <c r="A27" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="4"/>
     </row>
     <row r="28" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B28" s="5"/>
-    </row>
-    <row r="29" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
+      <c r="B28" s="4"/>
+    </row>
+    <row r="29" spans="1:2" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
     </row>
     <row r="30" spans="1:2" ht="21" x14ac:dyDescent="0.2">
-      <c r="A30" s="9" t="s">
-        <v>19</v>
+      <c r="A30" s="8" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="21" x14ac:dyDescent="0.2">
-      <c r="A31" s="9" t="s">
-        <v>15</v>
+      <c r="A31" s="8" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="21" x14ac:dyDescent="0.2">
-      <c r="A32" s="9" t="s">
-        <v>17</v>
+      <c r="A32" s="8" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="21" x14ac:dyDescent="0.2">
-      <c r="A33" s="9" t="s">
+      <c r="A33" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A36" s="6" t="s">
+    <row r="35" spans="1:2" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="8"/>
+    </row>
+    <row r="36" spans="1:2" s="10" customFormat="1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A36" s="9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A37" s="6" t="s">
+    <row r="37" spans="1:2" s="10" customFormat="1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A37" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A38" s="6" t="s">
+    <row r="38" spans="1:2" s="10" customFormat="1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A38" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A39" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A40" s="6"/>
+    <row r="39" spans="1:2" s="10" customFormat="1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A39" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="5"/>
     </row>
     <row r="41" spans="1:2" ht="21" x14ac:dyDescent="0.2">
-      <c r="A41" s="9" t="s">
+      <c r="A41" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="21" x14ac:dyDescent="0.2">
-      <c r="A42" s="9" t="s">
+      <c r="A42" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="8" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A44" s="2"/>
-      <c r="B44" s="7" t="s">
+      <c r="B44" s="6" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A45" s="2"/>
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A46" s="2"/>
-      <c r="B46" s="7" t="s">
+      <c r="B46" s="6" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A47" s="2"/>
-      <c r="B47" s="7" t="s">
+      <c r="B47" s="6" t="s">
         <v>3</v>
       </c>
     </row>

--- a/44_心理学/26_浥尘伙伴社团原创：通识教育/000 浥尘伙伴社团通识教育招生广告.xlsx
+++ b/44_心理学/26_浥尘伙伴社团原创：通识教育/000 浥尘伙伴社团通识教育招生广告.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\44_心理学\26_浥尘伙伴社团原创：通识教育\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75CEDBD6-6018-43CC-AD48-FD0F0A255CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A26C14E-8555-4B20-8B7D-8130D8276358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6465" yWindow="675" windowWidth="21600" windowHeight="11295" xr2:uid="{F9B5B54B-EA84-4F3E-A518-5A8438F4DD6B}"/>
+    <workbookView xWindow="12675" yWindow="3285" windowWidth="21600" windowHeight="11295" xr2:uid="{F9B5B54B-EA84-4F3E-A518-5A8438F4DD6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="20">
   <si>
     <t>微信公众号@浥尘伙伴社团</t>
   </si>
@@ -90,10 +90,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">        ■ 为什么越来越多的人抑郁躺平？</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">        ■ 为什么在网上人们会围观狗吃东西？</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -107,6 +103,14 @@
   </si>
   <si>
     <t xml:space="preserve">        ■ AI时代真正需要的能力是什么？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">解锁更多秘密，更有家长课堂……      </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">        ■ 为什么越来越多的人抑郁躺平出现心理疾病？</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -114,7 +118,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -189,6 +193,14 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -213,7 +225,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -246,6 +258,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -713,7 +728,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B1" s="4"/>
     </row>
@@ -729,12 +744,12 @@
     </row>
     <row r="4" spans="1:2" ht="21" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="21" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="21" x14ac:dyDescent="0.2">
@@ -744,11 +759,14 @@
     </row>
     <row r="7" spans="1:2" ht="21" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>18</v>
       </c>
     </row>
@@ -823,7 +841,7 @@
     </row>
     <row r="27" spans="1:2" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B27" s="4"/>
     </row>
@@ -839,12 +857,12 @@
     </row>
     <row r="30" spans="1:2" ht="21" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="21" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="21" x14ac:dyDescent="0.2">
@@ -854,11 +872,14 @@
     </row>
     <row r="33" spans="1:2" ht="21" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" s="11" t="s">
         <v>18</v>
       </c>
     </row>

--- a/44_心理学/26_浥尘伙伴社团原创：通识教育/000 浥尘伙伴社团通识教育招生广告.xlsx
+++ b/44_心理学/26_浥尘伙伴社团原创：通识教育/000 浥尘伙伴社团通识教育招生广告.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\44_心理学\26_浥尘伙伴社团原创：通识教育\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A26C14E-8555-4B20-8B7D-8130D8276358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C8ACF99-6EFE-473B-8D21-A10BD3DE0B7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12675" yWindow="3285" windowWidth="21600" windowHeight="11295" xr2:uid="{F9B5B54B-EA84-4F3E-A518-5A8438F4DD6B}"/>
+    <workbookView xWindow="8385" yWindow="2295" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{F9B5B54B-EA84-4F3E-A518-5A8438F4DD6B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="浥尘伙伴社团私塾" sheetId="1" r:id="rId1"/>
+    <sheet name="浥尘伙伴社团心理群" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="25">
   <si>
     <t>微信公众号@浥尘伙伴社团</t>
   </si>
@@ -111,6 +112,23 @@
   </si>
   <si>
     <t xml:space="preserve">        ■ 为什么越来越多的人抑郁躺平出现心理疾病？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>各位朋友大家好！</t>
+  </si>
+  <si>
+    <t>您是否为孩子成长中的心理问题所困扰？</t>
+  </si>
+  <si>
+    <t>我个人开设了一个儿童青少年心理健康微信群，可以为大家答疑解惑，同时也方便家长们交流探讨孩子们的心理健康问题。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">微信公众号：浥尘伙伴社团                 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>有兴趣的朋友可以扫码关注一下！</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -118,7 +136,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -197,6 +215,31 @@
     <font>
       <i/>
       <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color rgb="FF333333"/>
       <name val="微软雅黑"/>
       <family val="2"/>
@@ -225,7 +268,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -261,6 +304,15 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -395,6 +447,99 @@
             </a14:hiddenFill>
           </a:ext>
         </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>179294</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>3460000</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>26009</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49A482DB-92F4-3898-EEB3-09C053A60EDB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3832412"/>
+          <a:ext cx="3460000" cy="4833333"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>3697942</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>11208</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>6155085</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>115116</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="图片 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB3CC461-CB07-6ADB-DB40-F3C48C8E9A59}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3697942" y="5356414"/>
+          <a:ext cx="2457143" cy="2457143"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -959,4 +1104,142 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C29DDBBC-17F5-4EB1-8769-90D79872A090}">
+  <dimension ref="A1:A45"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="87" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="4"/>
+    </row>
+    <row r="2" spans="1:1" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="14"/>
+    </row>
+    <row r="4" spans="1:1" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="14"/>
+    </row>
+    <row r="6" spans="1:1" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="14"/>
+    </row>
+    <row r="8" spans="1:1" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="8"/>
+    </row>
+    <row r="10" spans="1:1" s="10" customFormat="1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A10" s="9"/>
+    </row>
+    <row r="11" spans="1:1" s="10" customFormat="1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A11" s="9"/>
+    </row>
+    <row r="12" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A12" s="2"/>
+    </row>
+    <row r="13" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A13" s="2"/>
+    </row>
+    <row r="14" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A14" s="2"/>
+    </row>
+    <row r="17" spans="1:1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A17" s="12"/>
+    </row>
+    <row r="18" spans="1:1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A18" s="13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="4"/>
+    </row>
+    <row r="21" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="7"/>
+    </row>
+    <row r="22" spans="1:1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="3"/>
+    </row>
+    <row r="23" spans="1:1" ht="21" x14ac:dyDescent="0.2">
+      <c r="A23" s="8"/>
+    </row>
+    <row r="24" spans="1:1" ht="21" x14ac:dyDescent="0.2">
+      <c r="A24" s="8"/>
+    </row>
+    <row r="25" spans="1:1" ht="21" x14ac:dyDescent="0.2">
+      <c r="A25" s="8"/>
+    </row>
+    <row r="26" spans="1:1" ht="21" x14ac:dyDescent="0.2">
+      <c r="A26" s="8"/>
+    </row>
+    <row r="27" spans="1:1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="8"/>
+    </row>
+    <row r="28" spans="1:1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="8"/>
+    </row>
+    <row r="29" spans="1:1" s="10" customFormat="1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A29" s="9"/>
+    </row>
+    <row r="30" spans="1:1" s="10" customFormat="1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A30" s="9"/>
+    </row>
+    <row r="31" spans="1:1" s="10" customFormat="1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A31" s="9"/>
+    </row>
+    <row r="32" spans="1:1" s="10" customFormat="1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A32" s="9"/>
+    </row>
+    <row r="33" spans="1:1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="5"/>
+    </row>
+    <row r="34" spans="1:1" ht="21" x14ac:dyDescent="0.2">
+      <c r="A34" s="8"/>
+    </row>
+    <row r="35" spans="1:1" ht="21" x14ac:dyDescent="0.2">
+      <c r="A35" s="8"/>
+    </row>
+    <row r="37" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A37" s="2"/>
+    </row>
+    <row r="38" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A38" s="2"/>
+    </row>
+    <row r="39" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A39" s="2"/>
+    </row>
+    <row r="40" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A40" s="2"/>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A45" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.70866141732283472" right="0.31496062992125984" top="0.39370078740157483" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>